--- a/software_developer_forms/003_software_product_demo_request_form--software_developer_forms.xlsx
+++ b/software_developer_forms/003_software_product_demo_request_form--software_developer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -781,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>company_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Company 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>demo_type</t>
+          <t>demo_type_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Demo Type</t>
+          <t>Demo Type 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>additional_comments_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Additional Comments 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -972,8 +972,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'software_product_option_1',_'value':_'option_value_1'}</t>
+          <t>option_value_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'software_product_option_1', 'value': 'option_value_1'}</t>
+          <t>option value 1</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'software_product_option_2',_'value':_'option_value_2'}</t>
+          <t>option_value_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'software_product_option_2', 'value': 'option_value_2'}</t>
+          <t>option value 2</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'software_product_option_3',_'value':_'option_value_3'}</t>
+          <t>option_value_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'software_product_option_3', 'value': 'option_value_3'}</t>
+          <t>option value 3</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'contact_person_option_1',_'value':_'contact_person_option_value_1'}</t>
+          <t>contact_person_option_value_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'contact_person_option_1', 'value': 'contact_person_option_value_1'}</t>
+          <t>contact person option value 1</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'contact_person_option_2',_'value':_'contact_person_option_value_2'}</t>
+          <t>contact_person_option_value_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'contact_person_option_2', 'value': 'contact_person_option_value_2'}</t>
+          <t>contact person option value 2</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'contact_person_option_3',_'value':_'contact_person_option_value_3'}</t>
+          <t>contact_person_option_value_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'contact_person_option_3', 'value': 'contact_person_option_value_3'}</t>
+          <t>contact person option value 3</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'software_version_option_1',_'value':_'software_version_option_value_1'}</t>
+          <t>software_version_option_value_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'software_version_option_1', 'value': 'software_version_option_value_1'}</t>
+          <t>software version option value 1</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'software_version_option_2',_'value':_'software_version_option_value_2'}</t>
+          <t>software_version_option_value_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'software_version_option_2', 'value': 'software_version_option_value_2'}</t>
+          <t>software version option value 2</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'software_version_option_3',_'value':_'software_version_option_value_3'}</t>
+          <t>software_version_option_value_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'software_version_option_3', 'value': 'software_version_option_value_3'}</t>
+          <t>software version option value 3</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'demo_schedule_option_1',_'value':_'demo_schedule_option_value_1'}</t>
+          <t>demo_schedule_option_value_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'demo_schedule_option_1', 'value': 'demo_schedule_option_value_1'}</t>
+          <t>demo schedule option value 1</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'demo_schedule_option_2',_'value':_'demo_schedule_option_value_2'}</t>
+          <t>demo_schedule_option_value_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'demo_schedule_option_2', 'value': 'demo_schedule_option_value_2'}</t>
+          <t>demo schedule option value 2</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'demo_schedule_option_3',_'value':_'demo_schedule_option_value_3'}</t>
+          <t>demo_schedule_option_value_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'demo_schedule_option_3', 'value': 'demo_schedule_option_value_3'}</t>
+          <t>demo schedule option value 3</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'demo_detailed_notes_option_1',_'value':_'demo_detailed_notes_option_value_1'}</t>
+          <t>demo_detailed_notes_option_value_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'demo_detailed_notes_option_1', 'value': 'demo_detailed_notes_option_value_1'}</t>
+          <t>demo detailed notes option value 1</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'demo_detailed_notes_option_2',_'value':_'demo_detailed_notes_option_value_2'}</t>
+          <t>demo_detailed_notes_option_value_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'demo_detailed_notes_option_2', 'value': 'demo_detailed_notes_option_value_2'}</t>
+          <t>demo detailed notes option value 2</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'demo_detailed_notes_option_3',_'value':_'demo_detailed_notes_option_value_3'}</t>
+          <t>demo_detailed_notes_option_value_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'demo_detailed_notes_option_3', 'value': 'demo_detailed_notes_option_value_3'}</t>
+          <t>demo detailed notes option value 3</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'demo_type_option_1',_'value':_'demo_type_option_value_1'}</t>
+          <t>demo_type_option_value_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'demo_type_option_1', 'value': 'demo_type_option_value_1'}</t>
+          <t>demo type option value 1</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'demo_type_option_2',_'value':_'demo_type_option_value_2'}</t>
+          <t>demo_type_option_value_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'demo_type_option_2', 'value': 'demo_type_option_value_2'}</t>
+          <t>demo type option value 2</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'demo_type_option_3',_'value':_'demo_type_option_value_3'}</t>
+          <t>demo_type_option_value_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'demo_type_option_3', 'value': 'demo_type_option_value_3'}</t>
+          <t>demo type option value 3</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'demo_length_option_1',_'value':_'demo_length_option_value_1'}</t>
+          <t>demo_length_option_value_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'demo_length_option_1', 'value': 'demo_length_option_value_1'}</t>
+          <t>demo length option value 1</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'demo_length_option_2',_'value':_'demo_length_option_value_2'}</t>
+          <t>demo_length_option_value_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'demo_length_option_2', 'value': 'demo_length_option_value_2'}</t>
+          <t>demo length option value 2</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'demo_length_option_3',_'value':_'demo_length_option_value_3'}</t>
+          <t>demo_length_option_value_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'demo_length_option_3', 'value': 'demo_length_option_value_3'}</t>
+          <t>demo length option value 3</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'demo_status_option_1',_'value':_'demo_status_option_value_1'}</t>
+          <t>demo_status_option_value_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'demo_status_option_1', 'value': 'demo_status_option_value_1'}</t>
+          <t>demo status option value 1</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'demo_status_option_2',_'value':_'demo_status_option_value_2'}</t>
+          <t>demo_status_option_value_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'demo_status_option_2', 'value': 'demo_status_option_value_2'}</t>
+          <t>demo status option value 2</t>
         </is>
       </c>
     </row>
@@ -1392,63 +1392,63 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'demo_status_option_3',_'value':_'demo_status_option_value_3'}</t>
+          <t>demo_status_option_value_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'demo_status_option_3', 'value': 'demo_status_option_value_3'}</t>
+          <t>demo status option value 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>demo_type_choices</t>
+          <t>demo_type_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_'demo_type_option_1',_'value':_'demo_type_option_value_1'}</t>
+          <t>demo_type_option_value_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 'demo_type_option_1', 'value': 'demo_type_option_value_1'}</t>
+          <t>demo type option value 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>demo_type_choices</t>
+          <t>demo_type_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_'demo_type_option_2',_'value':_'demo_type_option_value_2'}</t>
+          <t>demo_type_option_value_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 'demo_type_option_2', 'value': 'demo_type_option_value_2'}</t>
+          <t>demo type option value 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>demo_type_choices</t>
+          <t>demo_type_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'name':_'demo_type_option_3',_'value':_'demo_type_option_value_3'}</t>
+          <t>demo_type_option_value_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'name': 'demo_type_option_3', 'value': 'demo_type_option_value_3'}</t>
+          <t>demo type option value 3</t>
         </is>
       </c>
     </row>
